--- a/academias/Electricidad - Estadisticos 20221.xlsx
+++ b/academias/Electricidad - Estadisticos 20221.xlsx
@@ -519,10 +519,10 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -534,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -624,19 +624,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="H5" s="1">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="I5" s="2">
         <v>8</v>
@@ -732,25 +732,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -779,13 +779,13 @@
         <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -802,25 +802,25 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>69.23</v>
+        <v>92.31</v>
       </c>
       <c r="H10" s="1">
-        <v>30.77</v>
+        <v>7.69</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -834,19 +834,19 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>87.18000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
       <c r="I11" s="2">
         <v>7</v>
@@ -974,28 +974,28 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>86.84</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>13.16</v>
+        <v>12.82</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1096,25 +1096,28 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1131,22 +1134,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1163,22 +1169,25 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1192,25 +1201,28 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>96.77</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>3.23</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1227,22 +1239,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1259,22 +1274,25 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>93.33</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>6.67</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1291,22 +1309,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1323,22 +1344,25 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1355,22 +1379,25 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>34.62</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.9</v>
       </c>
       <c r="J10">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1384,25 +1411,28 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.4</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1419,22 +1449,25 @@
         <v>26</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>61.54</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>38.46</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.5</v>
       </c>
       <c r="J12">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1451,22 +1484,25 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F13">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.5</v>
       </c>
       <c r="J13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1483,22 +1519,25 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.7</v>
       </c>
       <c r="J14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1512,25 +1551,28 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>10.26</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.4</v>
       </c>
       <c r="J15">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1547,22 +1589,25 @@
         <v>26</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>15.38</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.9</v>
       </c>
       <c r="J16">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1628,10 +1673,10 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1643,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1678,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1713,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1733,22 +1778,22 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="H5" s="1">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="I5" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1771,19 +1816,19 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1818,7 +1863,7 @@
         <v>6.67</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1841,25 +1886,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1876,25 +1921,25 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>90</v>
+        <v>83.33</v>
       </c>
       <c r="H9" s="1">
-        <v>10</v>
+        <v>16.67</v>
       </c>
       <c r="I9" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1911,25 +1956,25 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>69.23</v>
+        <v>65.38</v>
       </c>
       <c r="H10" s="1">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1943,22 +1988,22 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>87.18000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="H11" s="1">
-        <v>12.82</v>
+        <v>17.5</v>
       </c>
       <c r="I11" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1981,16 +2026,16 @@
         <v>26</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>57.69</v>
+        <v>61.54</v>
       </c>
       <c r="H12" s="1">
-        <v>42.31</v>
+        <v>38.46</v>
       </c>
       <c r="I12" s="2">
         <v>6.7</v>
@@ -2028,7 +2073,7 @@
         <v>18.75</v>
       </c>
       <c r="I13" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2051,19 +2096,19 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="H14" s="1">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="I14" s="2">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2083,28 +2128,28 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>86.84</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>13.16</v>
+        <v>10.26</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2121,19 +2166,19 @@
         <v>26</v>
       </c>
       <c r="E16">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>65.38</v>
+        <v>84.62</v>
       </c>
       <c r="H16" s="1">
-        <v>34.62</v>
+        <v>15.38</v>
       </c>
       <c r="I16" s="2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20221.xlsx
+++ b/academias/Electricidad - Estadisticos 20221.xlsx
@@ -977,25 +977,25 @@
         <v>39</v>
       </c>
       <c r="E15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>12.82</v>
+        <v>10.26</v>
       </c>
       <c r="I15" s="2">
         <v>7.2</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1414,25 +1414,25 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H11" s="1">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="I11" s="2">
         <v>7.4</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1554,25 +1554,25 @@
         <v>39</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H15" s="1">
-        <v>10.26</v>
+        <v>7.69</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2131,25 +2131,25 @@
         <v>39</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H15" s="1">
-        <v>10.26</v>
+        <v>7.69</v>
       </c>
       <c r="I15" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>2.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20221.xlsx
+++ b/academias/Electricidad - Estadisticos 20221.xlsx
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>16.67</v>
       </c>
       <c r="I9" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1956,16 +1956,16 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>65.38</v>
+        <v>80.77</v>
       </c>
       <c r="H10" s="1">
-        <v>34.62</v>
+        <v>19.23</v>
       </c>
       <c r="I10" s="2">
         <v>7.2</v>

--- a/academias/Electricidad - Estadisticos 20221.xlsx
+++ b/academias/Electricidad - Estadisticos 20221.xlsx
@@ -1676,16 +1676,16 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>96.77</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="I2" s="2">
         <v>8.9</v>

--- a/academias/Electricidad - Estadisticos 20221.xlsx
+++ b/academias/Electricidad - Estadisticos 20221.xlsx
@@ -1676,19 +1676,19 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>96.77</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>3.23</v>
+        <v>12.9</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1746,19 +1746,19 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="I4" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1851,19 +1851,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H7" s="1">
-        <v>6.67</v>
+        <v>13.33</v>
       </c>
       <c r="I7" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>83.33</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
-        <v>16.67</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>26</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>80.77</v>
+        <v>76.92</v>
       </c>
       <c r="H10" s="1">
-        <v>19.23</v>
+        <v>23.08</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1991,19 +1991,19 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>82.5</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2026,19 +2026,19 @@
         <v>26</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>61.54</v>
+        <v>42.31</v>
       </c>
       <c r="H12" s="1">
-        <v>38.46</v>
+        <v>57.69</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2061,19 +2061,19 @@
         <v>32</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2096,19 +2096,19 @@
         <v>32</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2131,19 +2131,19 @@
         <v>39</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
       <c r="H15" s="1">
-        <v>7.69</v>
+        <v>15.38</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2166,19 +2166,19 @@
         <v>26</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>84.62</v>
+        <v>80.77</v>
       </c>
       <c r="H16" s="1">
-        <v>15.38</v>
+        <v>19.23</v>
       </c>
       <c r="I16" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J16">
         <v>0</v>
